--- a/data/trans_orig/IP2904-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70307</t>
+          <t>70697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>53135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71760</t>
+          <t>72063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110012</t>
+          <t>110286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137095</t>
+          <t>137792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>43689</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36867</t>
+          <t>36751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>55042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>69335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45710</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86312</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71249</t>
+          <t>70999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>91818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>89361</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111565</t>
+          <t>111697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167248</t>
+          <t>165915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199029</t>
+          <t>197712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58460</t>
+          <t>58756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74525</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99998</t>
+          <t>100390</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54503</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75006</t>
+          <t>75191</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49085</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69737</t>
+          <t>70209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110918</t>
+          <t>109288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140100</t>
+          <t>139513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>54856</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71886</t>
+          <t>72568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49802</t>
+          <t>49720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68251</t>
+          <t>68512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110697</t>
+          <t>111509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136735</t>
+          <t>135812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>24002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39316</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37378</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65502</t>
+          <t>65526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>88052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49854</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48972</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>68976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>92073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79181</t>
+          <t>78269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102317</t>
+          <t>103189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74791</t>
+          <t>75322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>97994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160728</t>
+          <t>161577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194390</t>
+          <t>194996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>32715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>52953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55768</t>
+          <t>54852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72270</t>
+          <t>73138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99138</t>
+          <t>99784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>53219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76333</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75436</t>
+          <t>76100</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113726</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>144418</t>
+          <t>145418</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>278296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317608</t>
+          <t>317733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288736</t>
+          <t>289489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329705</t>
+          <t>331745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578445</t>
+          <t>578726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>634669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>164861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>203473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>306843</t>
+          <t>306527</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>354995</t>
+          <t>353938</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>187317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225634</t>
+          <t>225327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182447</t>
+          <t>183005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220578</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>381633</t>
+          <t>382393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433063</t>
+          <t>433687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45079</t>
+          <t>44845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64682</t>
+          <t>65154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>52847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74534</t>
+          <t>73898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104793</t>
+          <t>104046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133076</t>
+          <t>133286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46070</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46816</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>63325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87816</t>
+          <t>87289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>33847</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54015</t>
+          <t>52671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>73544</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99652</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86806</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108727</t>
+          <t>109529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97995</t>
+          <t>97105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121641</t>
+          <t>121819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192144</t>
+          <t>191922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>225446</t>
+          <t>222961</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55218</t>
+          <t>54996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46527</t>
+          <t>46639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>67509</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87598</t>
+          <t>88961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116827</t>
+          <t>116449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44077</t>
+          <t>43337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>63018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88565</t>
+          <t>87798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117761</t>
+          <t>117180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64223</t>
+          <t>64206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84554</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67376</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87862</t>
+          <t>88283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138010</t>
+          <t>137480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>164625</t>
+          <t>165513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53073</t>
+          <t>53506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66862</t>
+          <t>67329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90812</t>
+          <t>92070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48318</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>29289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89882</t>
+          <t>89060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>88587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113375</t>
+          <t>112660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>92225</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115611</t>
+          <t>116125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186467</t>
+          <t>188969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221197</t>
+          <t>222290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41861</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64354</t>
+          <t>62541</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>42950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>63290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91446</t>
+          <t>89789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123240</t>
+          <t>119983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63472</t>
+          <t>64368</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>56952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83829</t>
+          <t>82819</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112468</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>303964</t>
+          <t>307035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>349135</t>
+          <t>350857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332471</t>
+          <t>333598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>377113</t>
+          <t>378764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650897</t>
+          <t>654035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>714500</t>
+          <t>716641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188361</t>
+          <t>187067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>172078</t>
+          <t>171519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332316</t>
+          <t>332666</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386578</t>
+          <t>386409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170323</t>
+          <t>168054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210176</t>
+          <t>207643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157398</t>
+          <t>155120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195737</t>
+          <t>195794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336186</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390196</t>
+          <t>388809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>60332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67998</t>
+          <t>67216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94189</t>
+          <t>94445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120607</t>
+          <t>122660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40673</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>72515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58559</t>
+          <t>58274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45005</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65931</t>
+          <t>64867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>88800</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116517</t>
+          <t>116706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79466</t>
+          <t>79087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100948</t>
+          <t>100359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88698</t>
+          <t>88693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>111768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174434</t>
+          <t>174701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205877</t>
+          <t>206368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37863</t>
+          <t>37963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56343</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79011</t>
+          <t>77453</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104421</t>
+          <t>104536</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53345</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73357</t>
+          <t>72784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58955</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81687</t>
+          <t>81417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118885</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151621</t>
+          <t>147666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82098</t>
+          <t>82262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68190</t>
+          <t>68175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136985</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166672</t>
+          <t>163738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45574</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30254</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62342</t>
+          <t>63887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86372</t>
+          <t>87319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52153</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54806</t>
+          <t>55212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77059</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102104</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72176</t>
+          <t>71602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>95202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76007</t>
+          <t>76067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131574</t>
+          <t>132315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164501</t>
+          <t>164703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78689</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64899</t>
+          <t>64696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88438</t>
+          <t>87817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126582</t>
+          <t>126618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157106</t>
+          <t>158211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>36529</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>57144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42809</t>
+          <t>42765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63859</t>
+          <t>63607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84163</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113853</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277523</t>
+          <t>275526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318552</t>
+          <t>315396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279414</t>
+          <t>277987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320163</t>
+          <t>324235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569025</t>
+          <t>565086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>626839</t>
+          <t>628218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>197553</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>170184</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>208488</t>
+          <t>208137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>342735</t>
+          <t>340659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>396319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182029</t>
+          <t>183560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222075</t>
+          <t>221708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202377</t>
+          <t>200266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396580</t>
+          <t>394293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>452493</t>
+          <t>453292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2904-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62100</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52419</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71213</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>61133</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51024</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70697</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>52641</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70565</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62100</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53135</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>72063</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110286</t>
+          <t>109556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137792</t>
+          <t>136217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45510</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37194</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56062</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35507</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27136</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43689</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27737</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45134</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>45510</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36751</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55042</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93890</t>
+          <t>93400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37365</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28487</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46615</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,15%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>35963</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27601</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44044</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>28043</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44481</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>37365</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>46608</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84959</t>
+          <t>85573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144975</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144975</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144975</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>132603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144975</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>144975</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>144975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100718</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90098</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112811</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>43,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>81754</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70999</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91818</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>71361</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91699</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>44,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100718</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>89361</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111697</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>48,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165915</t>
+          <t>168123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>198837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>48323</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39299</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58786</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28,17%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>38909</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31246</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>47142</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>30135</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>47797</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20,97%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>48323</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>39112</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>58756</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,15%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>74274</t>
+          <t>75081</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>101614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59672</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48298</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68951</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64911</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55077</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75191</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55668</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>75303</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>59672</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49652</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>70209</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109288</t>
+          <t>109703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139513</t>
+          <t>138777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>208713</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>185574</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>185574</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>185574</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>208713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59439</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>49553</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>68734</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>34,47%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>63446</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>54856</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>72568</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>54413</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>72072</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>46,9%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>53,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>59439</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>49720</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>68512</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111509</t>
+          <t>109171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135812</t>
+          <t>136060</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>44866</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35438</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53671</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>31156</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24002</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39569</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24494</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>38813</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44866</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35890</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53054</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65526</t>
+          <t>64944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88052</t>
+          <t>88019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39464</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31147</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49161</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>40681</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32846</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49057</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49564</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>30,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>39464</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>31548</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>48741</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92073</t>
+          <t>92522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>135283</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>135283</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>135283</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86540</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74777</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>97937</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>91165</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>78269</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>103189</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>79176</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>103207</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>86540</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>75322</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>97994</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>44,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161577</t>
+          <t>162310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194996</t>
+          <t>195895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45055</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36647</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>56113</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41388</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32715</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>52953</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32083</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>51823</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45055</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36310</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>54852</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73138</t>
+          <t>72425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99784</t>
+          <t>99707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>64930</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>54415</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>76619</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38,99%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>64324</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>53219</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>75498</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>53273</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>75619</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>64930</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>54846</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>76100</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113610</t>
+          <t>113606</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145418</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>196525</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>196525</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>196525</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>196877</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>196877</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>196877</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>196525</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>196525</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>196525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>308797</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>288011</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>328546</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>447</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>297498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>278296</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>317733</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>275889</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>319201</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>45,75%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>48,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>308797</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>289489</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>331745</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578726</t>
+          <t>577925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>634669</t>
+          <t>633820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>183754</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>165560</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>202309</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>146960</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>130223</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>164861</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>130030</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>163916</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>22,6%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>183754</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>164503</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>203473</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>306527</t>
+          <t>308439</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>353938</t>
+          <t>357243</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>201431</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>182824</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>221273</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>205878</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>187317</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>225327</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>184787</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>222901</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>31,66%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>201431</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>183005</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>220601</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382393</t>
+          <t>380426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433687</t>
+          <t>434364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63785</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54546</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74375</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>55251</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44845</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65154</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45420</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>64423</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>40,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>63785</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>73898</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104046</t>
+          <t>106108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133286</t>
+          <t>133661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37754</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28520</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47148</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36550</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28754</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47121</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28856</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46309</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37754</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29200</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>47513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63325</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87289</t>
+          <t>86171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34753</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53915</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43259</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33847</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51840</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>33867</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>53750</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>32,03%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43433</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34423</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73544</t>
+          <t>74022</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>100055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144972</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144972</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144972</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>135061</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>135061</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>135061</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>144972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109254</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96891</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122177</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>98500</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88287</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109529</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>87187</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>108989</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>50,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>55,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109254</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>97105</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121819</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>50,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191922</t>
+          <t>192695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222961</t>
+          <t>225498</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56648</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46138</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67899</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>44893</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36230</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>54996</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36184</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>54725</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>22,85%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,0%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>56648</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>46639</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67509</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>26,26%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>89059</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116449</t>
+          <t>116564</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49784</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40456</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60746</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>53043</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43337</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63018</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42952</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62798</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49784</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39783</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60637</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87798</t>
+          <t>88036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117180</t>
+          <t>117921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>215686</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>215686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>215686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>196436</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>196436</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>196436</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>215686</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>215686</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>215686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77797</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67019</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87060</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>48,99%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>73902</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>64206</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84008</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>64124</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>83768</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>49,88%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>43,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>56,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67156</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>88283</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>48,99%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137480</t>
+          <t>137840</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>165513</t>
+          <t>165518</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43719</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36061</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54033</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>34597</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27030</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>44156</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26545</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43426</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43719</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34949</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53506</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67329</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92070</t>
+          <t>90885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37281</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29126</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39674</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31644</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48780</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32018</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37281</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>29289</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>46444</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64846</t>
+          <t>65994</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89060</t>
+          <t>90328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158796</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158796</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158796</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>148173</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>148173</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>148173</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158796</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158796</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104021</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>92644</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>116384</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>100661</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>88587</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>112660</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>87021</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>112889</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>104021</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>92225</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>116125</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188969</t>
+          <t>188508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222290</t>
+          <t>223112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,77%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>53639</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43819</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>64606</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>51730</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40944</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>62541</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>42005</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>64194</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>25,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>53639</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42950</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>63290</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89789</t>
+          <t>89791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119983</t>
+          <t>119825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35553</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>55993</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,51%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>51934</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>42017</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>64368</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>42050</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>64610</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>25,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>45346</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>35784</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>56952</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>81928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113074</t>
+          <t>112640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>203006</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>203006</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>203006</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>204325</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>204325</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>204325</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>203006</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>203006</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>203006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>354857</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>332377</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>375027</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>49,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>46,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>51,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>328315</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>307035</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>350857</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>307161</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>348445</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>48,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>354857</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>333598</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>378764</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>49,12%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>654035</t>
+          <t>653849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>716641</t>
+          <t>719828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>191760</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>173106</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>210210</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>167770</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>149475</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>187067</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>149188</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>186155</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>191760</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>171519</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>211044</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332666</t>
+          <t>333220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386409</t>
+          <t>385400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>175843</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>157093</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>195180</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>21,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>168054</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>207643</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>168498</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>207282</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>27,47%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>175843</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>155120</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>195794</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335471</t>
+          <t>336730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388809</t>
+          <t>388580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57513</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46845</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67456</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>50385</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41335</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60332</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41358</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59786</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57513</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>67216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94445</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40937</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28765</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20897</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37715</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21445</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37718</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31475</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23544</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40091</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48129</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72515</t>
+          <t>72514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54320</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>44129</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64197</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30,79%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>44,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48989</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39585</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>58274</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>40654</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>57873</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>38,23%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>54320</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>44488</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64867</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88800</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116706</t>
+          <t>117392</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>143308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143308</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143308</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>128138</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>128138</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>128138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>143308</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>143308</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>143308</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100219</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88394</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112085</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>90015</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>79087</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>100359</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>79906</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100959</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,11%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100219</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88693</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111768</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174701</t>
+          <t>175081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206368</t>
+          <t>206867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36178</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>55325</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25,79%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46640</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37963</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>56441</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>37779</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>56503</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>23,38%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44458</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>34781</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>53700</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>78358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104536</t>
+          <t>104641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69846</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58183</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80719</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>62871</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53282</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>72784</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52739</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>73797</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>69846</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>59499</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>81417</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118361</t>
+          <t>118698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147666</t>
+          <t>146729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>214523</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>214523</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>214523</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>199527</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>199527</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>199527</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>214523</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>214523</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>214523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>78280</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67688</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>88890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>48,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>54,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>72273</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>63195</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>82262</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>63106</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>82008</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>47,33%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>41,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>53,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>78280</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>68175</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>88671</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>48,29%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135861</t>
+          <t>137116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163738</t>
+          <t>164797</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37904</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29624</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47407</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>36798</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29341</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>45985</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29166</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>45524</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37904</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29153</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>47426</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63887</t>
+          <t>63190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87319</t>
+          <t>87270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45927</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36903</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56289</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43635</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34985</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51831</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34907</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>52700</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45927</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36469</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55212</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77674</t>
+          <t>77163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102958</t>
+          <t>103747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152706</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152706</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152706</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>162111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>64374</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53377</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>75399</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>83670</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71602</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95202</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>95189</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>64374</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54656</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76067</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,46%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132315</t>
+          <t>130516</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164703</t>
+          <t>163349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>64281</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>86685</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>66607</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56092</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>77354</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>55791</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>78723</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>75424</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>64696</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>87817</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126618</t>
+          <t>126897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158211</t>
+          <t>157487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52594</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>42083</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>62882</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>46112</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>36529</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57144</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>36629</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>56377</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>23,48%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>18,6%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>52594</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>42765</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>63607</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>27,34%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84199</t>
+          <t>84948</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113082</t>
+          <t>114155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>192393</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>192393</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>192393</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>196389</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>196389</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>196389</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>192393</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>192393</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>192393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>300387</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>280570</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>323746</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>42,17%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>296343</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>275526</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>315396</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>276218</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>319409</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>43,79%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>300387</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>277987</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>324235</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>565086</t>
+          <t>565277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628218</t>
+          <t>624509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>189261</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>168915</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>208042</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>178810</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>160146</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>197553</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>160581</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197992</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>189261</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>170292</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>208137</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>340659</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>396319</t>
+          <t>396503</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>222687</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>202016</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>243441</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>201607</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>183560</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>221708</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>184040</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>222837</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>29,79%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>222687</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>200266</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>242740</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394293</t>
+          <t>397030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453292</t>
+          <t>453558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
